--- a/data_extactor/batch_10_fa/trimmed/batch_0051_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0051_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و مردم‌شناسی | امور اداری و دفتری | روان‌شناسی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | اداری | روان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | کارشناسان آموزش سلامت | مددکاران اجتماعی حوزه سلامت | کارشناسان مدارک پزشکی | منشی‌ها و دستیاران اداری پزشکی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | پزشکی و دندان‌پزشکی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | حقوق و مقررات دولتی</t>
+          <t>رایانه و الکترونیک | پزشکی و دندان‌پزشکی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | کارشناسان مدیریت اسناد | کارشناسان انفورماتیک سلامت | کارشناسان مدارک پزشکی | مدیران خدمات بهداشتی و درمانی</t>
+          <t>مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متخصصان انفورماتیک سلامت | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | آموزش و تدریس | زیست‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | آموزش و پرورش | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کایروپراکتیک‌ها | مربیان و استعداد‌یابان ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | پزشکان طب فیزیکی و توان‌بخشی | فیزیوتراپ‌ها | پزشکان متخصص طب ورزشی</t>
+          <t>کایروپراکتورها / متخصصان درمان دستی | مربیان و استعدادیابان ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | پزشکان طب ورزشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | علوم پایه | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاوره | پزشکان عمومی و خانواده | متخصصان مغز و اعصاب | ماماها | متخصصان زنان و زایمان | پزشکان متخصص اطفال | پزشکان طب پیشگیری</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان عمومی و خانواده | متخصصان مغز و اعصاب | ماماهای پرستار | متخصصان زنان و زایمان | متخصصان عمومی کودکان | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | ثبات دست و بازو | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | دقت کنترل | چابکی دستی</t>
+          <t>درک شفاهی | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | مهارت دستی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | متخصصان جراحی ارتوپدی | جراحان اطفال | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | زیست‌شناسی | حقوق و مقررات دولتی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | زیست‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان مدارک پزشکی | کارشناسان امور بیماران و پذیرش | دستیاران جراحی | پرستاران رسمی | بهیاران و کمک‌پرستاران دارای مجوز | سایر تکنسین‌ها و کاردان‌های حوزه سلامت</t>
+          <t>کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان امور بیماران و پذیرش | دستیاران جراحی | پرستاران | بهیاران و کمک‌پرستاران دارای مجوز | سایر متخصصان و تکنسین‌های حوزه سلامت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | زیست‌شناسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | زیست‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماپرستاران | متخصصان زنان و زایمان | پزشکان متخصص اطفال | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | متخصصان زنان و زایمان | متخصصان عمومی کودکان | پرستاران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پرستاران | دستیاران کاردرمانی | مراقبان خدمات شخصی | دستیاران فیزیوتراپی | پرستاران رسمی</t>
+          <t>تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پرستاران | کاردان‌های کاردرمانی | مراقبان خدمات شخصی و همراهان توان‌خواهان | کاردان‌های فیزیوتراپی | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حمل‌ونقل و ترابری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | حمل و نقل | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مربیان و مراقبان کودک | سرپرستان رده‌اول ارائه‌دهندگان خدمات فردی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پرستاران | کمک‌فیزیوتراپ‌ها | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مربیان و مراقبان کودک | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پرستاران | کمک‌یاران فیزیوتراپی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و تدریس | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | قدرت ایستا | قدرت تنه | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | قدرت ایستا | قدرت تنه | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | متصدیان خدمات عمومی بیمارستان (خدمات) | کمک‌فیزیوتراپ‌ها | بهیاران روان‌پزشکی | پرستاران رسمی</t>
+          <t>تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | خدمات‌دهندگان و انتقال‌دهندگان بیمار | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
